--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +883,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +948,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1013,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1078,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1143,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1334,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1399,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1464,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1529,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1594,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1659,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1724,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1742,65 +1806,130 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>3084-86-SE26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.967.700-5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>51562.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>3515-294-CM26</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>69.060.300-4</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>CLOUDLATAM SPA</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>150600.45</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
